--- a/data/trans_dic/IQ26A_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ26A_R2-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>14,99%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,73%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12,44%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24,96%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 21,72</t>
+          <t>6,6; 17,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,74; 19,26</t>
+          <t>4,86; 14,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 20,17</t>
+          <t>8,49; 21,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 39,12</t>
+          <t>4,1; 23,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 17,92</t>
+          <t>9,77; 21,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 15,12</t>
+          <t>7,0; 19,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 20,85</t>
+          <t>6,98; 19,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 21,34</t>
+          <t>13,84; 40,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 17,75</t>
+          <t>9,68; 18,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 14,7</t>
+          <t>6,95; 15,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 17,58</t>
+          <t>9,51; 18,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 25,23</t>
+          <t>11,09; 26,94</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20,66%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>14,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,07%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 21,58</t>
+          <t>9,62; 22,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 15,88</t>
+          <t>4,33; 14,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 21,28</t>
+          <t>10,9; 22,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,86; 40,53</t>
+          <t>7,5; 38,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 21,15</t>
+          <t>8,64; 21,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 14,53</t>
+          <t>5,67; 16,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 22,21</t>
+          <t>10,24; 21,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 39,97</t>
+          <t>13,96; 42,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,81</t>
+          <t>10,72; 19,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 13,68</t>
+          <t>6,38; 13,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,77; 20,01</t>
+          <t>11,34; 19,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,14; 35,41</t>
+          <t>14,95; 35,64</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,85%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,34%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8,12%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 15,56</t>
+          <t>3,72; 12,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 20,87</t>
+          <t>4,03; 13,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 14,53</t>
+          <t>7,98; 21,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 60,49</t>
+          <t>3,42; 33,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 12,21</t>
+          <t>4,05; 15,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 13,74</t>
+          <t>8,41; 21,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 22,1</t>
+          <t>3,85; 14,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 35,08</t>
+          <t>10,84; 53,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,49</t>
+          <t>4,98; 11,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,7; 15,68</t>
+          <t>7,68; 16,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 16,45</t>
+          <t>7,53; 16,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,53; 36,74</t>
+          <t>9,34; 36,45</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,59%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 17,23</t>
+          <t>7,97; 15,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,9</t>
+          <t>8,38; 15,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 18,7</t>
+          <t>11,62; 19,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,13; 42,37</t>
+          <t>7,11; 28,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 15,41</t>
+          <t>9,6; 17,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,67</t>
+          <t>7,37; 14,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 19,39</t>
+          <t>10,96; 18,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 26,74</t>
+          <t>10,33; 34,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 14,78</t>
+          <t>9,5; 14,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,14</t>
+          <t>8,87; 14,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,76</t>
+          <t>12,11; 17,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 30,39</t>
+          <t>10,36; 26,21</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>12,76%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,28%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,76%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 18,97</t>
+          <t>6,7; 15,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,37</t>
+          <t>9,21; 19,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 16,62</t>
+          <t>10,55; 20,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 38,2</t>
+          <t>20,59; 47,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 15,77</t>
+          <t>7,89; 18,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 19,18</t>
+          <t>4,64; 11,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,45; 20,5</t>
+          <t>7,71; 16,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 49,99</t>
+          <t>12,43; 41,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 15,16</t>
+          <t>8,49; 15,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,92</t>
+          <t>7,86; 13,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 16,84</t>
+          <t>10,35; 16,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 39,46</t>
+          <t>20,65; 41,77</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>18,17%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,9%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>24,96%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,91; 27,17</t>
+          <t>15,49; 31,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 14,78</t>
+          <t>6,18; 18,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,47; 34,54</t>
+          <t>7,25; 20,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,59; 47,07</t>
+          <t>3,28; 31,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,44; 31,04</t>
+          <t>12,0; 27,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,14; 19,06</t>
+          <t>2,34; 14,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 20,73</t>
+          <t>16,71; 36,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 27,13</t>
+          <t>5,75; 49,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,75; 26,08</t>
+          <t>15,14; 26,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,96</t>
+          <t>5,32; 14,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,27; 25,25</t>
+          <t>13,49; 25,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 26,59</t>
+          <t>7,05; 28,86</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12,1%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13,65%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10,1%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>14,14%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,41; 15,82</t>
+          <t>10,29; 14,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,14</t>
+          <t>8,99; 12,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,05; 16,45</t>
+          <t>12,39; 16,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,26; 31,88</t>
+          <t>14,11; 24,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,48</t>
+          <t>11,6; 15,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,8</t>
+          <t>8,35; 12,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,52; 16,96</t>
+          <t>12,17; 16,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,64; 23,51</t>
+          <t>18,49; 30,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,41; 14,37</t>
+          <t>11,51; 14,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,83</t>
+          <t>9,07; 11,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,99; 16,18</t>
+          <t>12,94; 16,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,0; 25,1</t>
+          <t>17,41; 25,13</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11068</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13471</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>15235</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10163</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9948</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11068</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7756</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13471</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11803</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10123; 22067</t>
+          <t>6352; 16610</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5837; 16691</t>
+          <t>4142; 12736</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5802; 16134</t>
+          <t>8247; 20474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4164; 11766</t>
+          <t>1508; 8479</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6432; 17248</t>
+          <t>9931; 21897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4215; 12877</t>
+          <t>6069; 17026</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8093; 20262</t>
+          <t>5580; 15792</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1500; 8039</t>
+          <t>4170; 12244</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19286; 35127</t>
+          <t>19158; 35680</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11832; 25265</t>
+          <t>11935; 25809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16152; 31142</t>
+          <t>16839; 32157</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6678; 17090</t>
+          <t>7423; 18028</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12611</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8097</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17878</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4114</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12253</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9009</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>15471</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6496</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12611</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8097</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17878</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10760</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7625; 18420</t>
+          <t>8270; 18977</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4988; 14505</t>
+          <t>4013; 13678</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10845; 21848</t>
+          <t>12065; 25018</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3375; 9872</t>
+          <t>1493; 7756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8008; 18182</t>
+          <t>7370; 18131</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4515; 13473</t>
+          <t>5177; 15386</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11539; 24584</t>
+          <t>10515; 22028</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1806; 8492</t>
+          <t>3473; 10590</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18216; 33941</t>
+          <t>18359; 33070</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11657; 25171</t>
+          <t>11737; 25150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25120; 42693</t>
+          <t>24204; 41526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6447; 16148</t>
+          <t>6697; 15961</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6612</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10427</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5844</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11957</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5023</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7255</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6612</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10427</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5668</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3018; 10282</t>
+          <t>3692; 12674</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7519; 17405</t>
+          <t>3343; 11381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2403; 8988</t>
+          <t>5915; 15849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1160; 6992</t>
+          <t>542; 5305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3770; 12133</t>
+          <t>2676; 10001</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3608; 11379</t>
+          <t>7017; 17744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5991; 16375</t>
+          <t>2380; 8720</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>729; 5807</t>
+          <t>1285; 6317</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8473; 19003</t>
+          <t>8235; 19453</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12797; 26070</t>
+          <t>12771; 26594</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10178; 22356</t>
+          <t>10240; 22551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3241; 10327</t>
+          <t>2587; 10094</t>
         </is>
       </c>
     </row>
@@ -2415,37 +2415,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21811</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6683</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>25503</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>21041</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>31737</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8644</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21811</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25501</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31568</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>13784</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18894; 33806</t>
+          <t>15798; 30042</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14520; 29585</t>
+          <t>18240; 34564</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24983; 40918</t>
+          <t>24363; 40616</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4455; 15554</t>
+          <t>3013; 12039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15642; 30536</t>
+          <t>18825; 34579</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18260; 34107</t>
+          <t>14643; 28733</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23369; 40649</t>
+          <t>23982; 40906</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3124; 12490</t>
+          <t>3593; 11952</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36311; 58310</t>
+          <t>37456; 57951</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36600; 58846</t>
+          <t>36926; 58309</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51850; 76103</t>
+          <t>51901; 76830</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10030; 25352</t>
+          <t>7992; 20220</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13285</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19006</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21146</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13147</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>12835</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10500</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>15880</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13285</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21146</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>17947</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7870; 19080</t>
+          <t>8350; 19149</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6504; 16405</t>
+          <t>12771; 26544</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10393; 22435</t>
+          <t>14990; 29283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2283; 8858</t>
+          <t>8132; 18868</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8490; 19639</t>
+          <t>7941; 18995</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12844; 26598</t>
+          <t>6691; 16635</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14849; 29125</t>
+          <t>10413; 22099</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8459; 20947</t>
+          <t>2479; 8366</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19009; 34133</t>
+          <t>19118; 35511</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21482; 39371</t>
+          <t>22243; 39234</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28571; 46656</t>
+          <t>28674; 46655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12250; 25681</t>
+          <t>12270; 24828</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15524</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7858</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8520</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>13474</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3540</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>15096</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15524</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7858</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8520</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5434</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8832; 20143</t>
+          <t>10767; 21567</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1389; 7576</t>
+          <t>4374; 13203</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9963; 20893</t>
+          <t>4920; 14228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>858; 6128</t>
+          <t>682; 6550</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10034; 21576</t>
+          <t>8897; 20154</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4346; 13483</t>
+          <t>1199; 7414</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4497; 14062</t>
+          <t>10110; 22176</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>677; 6388</t>
+          <t>786; 6711</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22617; 37464</t>
+          <t>21750; 37545</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6382; 17032</t>
+          <t>6486; 17922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17028; 32406</t>
+          <t>17314; 32535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2454; 9724</t>
+          <t>2430; 9948</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>81555</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>74830</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>103010</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>85144</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>66210</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>93155</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>33892</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>81555</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>74830</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>103010</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>67978</t>
+          <t>65397</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>71173; 98706</t>
+          <t>69338; 96382</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>54270; 79551</t>
+          <t>61829; 88996</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79369; 108404</t>
+          <t>86887; 118048</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25369; 44284</t>
+          <t>24727; 42530</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68980; 97566</t>
+          <t>72391; 99466</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61757; 88052</t>
+          <t>54758; 80159</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87802; 118967</t>
+          <t>80197; 108910</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25587; 44106</t>
+          <t>24999; 41038</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>148111; 186449</t>
+          <t>149404; 187970</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122049; 158967</t>
+          <t>121888; 159837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>176709; 220055</t>
+          <t>176053; 218946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55511; 81958</t>
+          <t>54049; 78007</t>
         </is>
       </c>
     </row>
